--- a/테이블구조.xlsx
+++ b/테이블구조.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\students\강정호\til-dbms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28A6152-BA29-42A9-AB5D-FD054682F256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7433A1CC-B0E0-4F9A-943F-26B2A4448B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15750" xr2:uid="{0940A7DE-0F31-4741-ABF7-BC78978B57D6}"/>
   </bookViews>
@@ -390,15 +390,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>후보키</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>값이 자동으로 증가</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>필수 값</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>후보키 : 기본키가 될 수 있는 값</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -406,7 +406,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -440,14 +440,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="0"/>
@@ -457,7 +449,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -472,7 +464,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -863,6 +861,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -931,24 +947,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1277,7 +1275,7 @@
     <col min="13" max="13" width="15.125" style="7" bestFit="1" customWidth="1"/>
     <col min="14" max="17" width="9" style="7"/>
     <col min="18" max="18" width="20.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="21.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="30.125" style="7" bestFit="1" customWidth="1"/>
     <col min="20" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
@@ -1292,55 +1290,55 @@
       <c r="F2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="30">
+      <c r="G2" s="36">
         <v>45712</v>
       </c>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="32"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="38"/>
       <c r="K2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="L2" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="34"/>
+      <c r="M2" s="40"/>
     </row>
     <row r="3" spans="4:19" x14ac:dyDescent="0.3">
       <c r="D3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="37"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="43"/>
       <c r="K3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="L3" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="17"/>
+      <c r="M3" s="23"/>
     </row>
     <row r="4" spans="4:19" x14ac:dyDescent="0.3">
       <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="17"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="23"/>
     </row>
     <row r="5" spans="4:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D5" s="4" t="s">
@@ -1386,7 +1384,7 @@
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>41</v>
@@ -1397,11 +1395,11 @@
       <c r="M6" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="R6" s="38" t="s">
+      <c r="R6" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="S6" s="39" t="s">
-        <v>84</v>
+      <c r="S6" s="18" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="4:19" x14ac:dyDescent="0.3">
@@ -1418,7 +1416,7 @@
         <v>3</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I7" s="11"/>
       <c r="J7" s="11" t="s">
@@ -1427,10 +1425,10 @@
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
       <c r="M7" s="12"/>
-      <c r="R7" s="40" t="s">
+      <c r="R7" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="S7" s="41" t="s">
+      <c r="S7" s="19" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1448,17 +1446,17 @@
         <v>50</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I8" s="11"/>
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
       <c r="M8" s="12"/>
-      <c r="R8" s="40" t="s">
+      <c r="R8" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="S8" s="41" t="s">
+      <c r="S8" s="19" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1476,7 +1474,7 @@
         <v>20</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I9" s="11"/>
       <c r="J9" s="11"/>
@@ -1485,10 +1483,10 @@
       </c>
       <c r="L9" s="11"/>
       <c r="M9" s="12"/>
-      <c r="R9" s="40" t="s">
+      <c r="R9" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="S9" s="41" t="s">
+      <c r="S9" s="19" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1506,18 +1504,18 @@
         <v>100</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I10" s="11"/>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
       <c r="M10" s="12"/>
-      <c r="R10" s="40" t="s">
+      <c r="R10" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="S10" s="41" t="s">
-        <v>82</v>
+      <c r="S10" s="19" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="4:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1534,7 +1532,7 @@
         <v>50</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
@@ -1543,11 +1541,11 @@
       </c>
       <c r="L11" s="11"/>
       <c r="M11" s="12"/>
-      <c r="R11" s="42" t="s">
+      <c r="R11" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="S11" s="43" t="s">
-        <v>83</v>
+      <c r="S11" s="20" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="4:19" x14ac:dyDescent="0.3">
@@ -1564,7 +1562,7 @@
         <v>39</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
@@ -1575,68 +1573,68 @@
       </c>
     </row>
     <row r="13" spans="4:19" x14ac:dyDescent="0.3">
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="20"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="26"/>
     </row>
     <row r="14" spans="4:19" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D14" s="21" t="s">
+      <c r="D14" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="23"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="29"/>
     </row>
     <row r="15" spans="4:19" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D15" s="24"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="26"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="32"/>
     </row>
     <row r="16" spans="4:19" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D16" s="24"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="26"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="32"/>
     </row>
     <row r="17" spans="4:13" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D17" s="27"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="28"/>
-      <c r="M17" s="29"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="35"/>
     </row>
     <row r="18" spans="4:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="19" spans="4:13" x14ac:dyDescent="0.3">
@@ -1649,55 +1647,55 @@
       <c r="F19" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G19" s="30">
+      <c r="G19" s="36">
         <v>45712</v>
       </c>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="32"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="38"/>
       <c r="K19" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L19" s="33" t="s">
+      <c r="L19" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="M19" s="34"/>
+      <c r="M19" s="40"/>
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D20" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="35" t="s">
+      <c r="E20" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="37"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="43"/>
       <c r="K20" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="15" t="s">
+      <c r="L20" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="M20" s="17"/>
+      <c r="M20" s="23"/>
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="17"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="23"/>
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D22" s="4" t="s">
@@ -1745,7 +1743,7 @@
         <v>3</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I23" s="11" t="s">
         <v>41</v>
@@ -1769,7 +1767,7 @@
         <v>10</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I24" s="10"/>
       <c r="J24" s="10"/>
@@ -1838,68 +1836,68 @@
       <c r="M29" s="14"/>
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="20"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
+      <c r="M30" s="26"/>
     </row>
     <row r="31" spans="4:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D31" s="21" t="s">
+      <c r="D31" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
-      <c r="M31" s="23"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="28"/>
+      <c r="J31" s="28"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+      <c r="M31" s="29"/>
     </row>
     <row r="32" spans="4:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D32" s="24"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="25"/>
-      <c r="J32" s="25"/>
-      <c r="K32" s="25"/>
-      <c r="L32" s="25"/>
-      <c r="M32" s="26"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="32"/>
     </row>
     <row r="33" spans="4:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D33" s="24"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="25"/>
-      <c r="J33" s="25"/>
-      <c r="K33" s="25"/>
-      <c r="L33" s="25"/>
-      <c r="M33" s="26"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="32"/>
     </row>
     <row r="34" spans="4:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D34" s="27"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="28"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
-      <c r="M34" s="29"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="34"/>
+      <c r="K34" s="34"/>
+      <c r="L34" s="34"/>
+      <c r="M34" s="35"/>
     </row>
     <row r="35" spans="4:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
@@ -1912,55 +1910,55 @@
       <c r="F36" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G36" s="30">
+      <c r="G36" s="36">
         <v>45712</v>
       </c>
-      <c r="H36" s="31"/>
-      <c r="I36" s="31"/>
-      <c r="J36" s="32"/>
+      <c r="H36" s="37"/>
+      <c r="I36" s="37"/>
+      <c r="J36" s="38"/>
       <c r="K36" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L36" s="33" t="s">
+      <c r="L36" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="M36" s="34"/>
+      <c r="M36" s="40"/>
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D37" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E37" s="35" t="s">
+      <c r="E37" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="F37" s="36"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="36"/>
-      <c r="I37" s="36"/>
-      <c r="J37" s="37"/>
+      <c r="F37" s="42"/>
+      <c r="G37" s="42"/>
+      <c r="H37" s="42"/>
+      <c r="I37" s="42"/>
+      <c r="J37" s="43"/>
       <c r="K37" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="L37" s="15" t="s">
+      <c r="L37" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="M37" s="17"/>
+      <c r="M37" s="23"/>
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D38" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="E38" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="17"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="23"/>
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D39" s="4" t="s">
@@ -2008,7 +2006,7 @@
         <v>39</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I40" s="11" t="s">
         <v>41</v>
@@ -2034,7 +2032,7 @@
         <v>50</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I41" s="11"/>
       <c r="J41" s="11"/>
@@ -2076,7 +2074,7 @@
         <v>39</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I43" s="11"/>
       <c r="J43" s="11"/>
@@ -2121,68 +2119,68 @@
       <c r="M46" s="12"/>
     </row>
     <row r="47" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D47" s="18" t="s">
+      <c r="D47" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="19"/>
-      <c r="J47" s="19"/>
-      <c r="K47" s="19"/>
-      <c r="L47" s="19"/>
-      <c r="M47" s="20"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="25"/>
+      <c r="I47" s="25"/>
+      <c r="J47" s="25"/>
+      <c r="K47" s="25"/>
+      <c r="L47" s="25"/>
+      <c r="M47" s="26"/>
     </row>
     <row r="48" spans="4:13" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D48" s="21" t="s">
+      <c r="D48" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="E48" s="22"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="22"/>
-      <c r="H48" s="22"/>
-      <c r="I48" s="22"/>
-      <c r="J48" s="22"/>
-      <c r="K48" s="22"/>
-      <c r="L48" s="22"/>
-      <c r="M48" s="23"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="28"/>
+      <c r="I48" s="28"/>
+      <c r="J48" s="28"/>
+      <c r="K48" s="28"/>
+      <c r="L48" s="28"/>
+      <c r="M48" s="29"/>
     </row>
     <row r="49" spans="4:13" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D49" s="24"/>
-      <c r="E49" s="25"/>
-      <c r="F49" s="25"/>
-      <c r="G49" s="25"/>
-      <c r="H49" s="25"/>
-      <c r="I49" s="25"/>
-      <c r="J49" s="25"/>
-      <c r="K49" s="25"/>
-      <c r="L49" s="25"/>
-      <c r="M49" s="26"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="31"/>
+      <c r="I49" s="31"/>
+      <c r="J49" s="31"/>
+      <c r="K49" s="31"/>
+      <c r="L49" s="31"/>
+      <c r="M49" s="32"/>
     </row>
     <row r="50" spans="4:13" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D50" s="24"/>
-      <c r="E50" s="25"/>
-      <c r="F50" s="25"/>
-      <c r="G50" s="25"/>
-      <c r="H50" s="25"/>
-      <c r="I50" s="25"/>
-      <c r="J50" s="25"/>
-      <c r="K50" s="25"/>
-      <c r="L50" s="25"/>
-      <c r="M50" s="26"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="31"/>
+      <c r="F50" s="31"/>
+      <c r="G50" s="31"/>
+      <c r="H50" s="31"/>
+      <c r="I50" s="31"/>
+      <c r="J50" s="31"/>
+      <c r="K50" s="31"/>
+      <c r="L50" s="31"/>
+      <c r="M50" s="32"/>
     </row>
     <row r="51" spans="4:13" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D51" s="27"/>
-      <c r="E51" s="28"/>
-      <c r="F51" s="28"/>
-      <c r="G51" s="28"/>
-      <c r="H51" s="28"/>
-      <c r="I51" s="28"/>
-      <c r="J51" s="28"/>
-      <c r="K51" s="28"/>
-      <c r="L51" s="28"/>
-      <c r="M51" s="29"/>
+      <c r="D51" s="33"/>
+      <c r="E51" s="34"/>
+      <c r="F51" s="34"/>
+      <c r="G51" s="34"/>
+      <c r="H51" s="34"/>
+      <c r="I51" s="34"/>
+      <c r="J51" s="34"/>
+      <c r="K51" s="34"/>
+      <c r="L51" s="34"/>
+      <c r="M51" s="35"/>
     </row>
     <row r="52" spans="4:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="53" spans="4:13" x14ac:dyDescent="0.3">
@@ -2195,55 +2193,55 @@
       <c r="F53" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G53" s="30">
+      <c r="G53" s="36">
         <v>45712</v>
       </c>
-      <c r="H53" s="31"/>
-      <c r="I53" s="31"/>
-      <c r="J53" s="32"/>
+      <c r="H53" s="37"/>
+      <c r="I53" s="37"/>
+      <c r="J53" s="38"/>
       <c r="K53" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L53" s="33" t="s">
+      <c r="L53" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="M53" s="34"/>
+      <c r="M53" s="40"/>
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D54" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E54" s="35" t="s">
+      <c r="E54" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="F54" s="36"/>
-      <c r="G54" s="36"/>
-      <c r="H54" s="36"/>
-      <c r="I54" s="36"/>
-      <c r="J54" s="37"/>
+      <c r="F54" s="42"/>
+      <c r="G54" s="42"/>
+      <c r="H54" s="42"/>
+      <c r="I54" s="42"/>
+      <c r="J54" s="43"/>
       <c r="K54" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="L54" s="15" t="s">
+      <c r="L54" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="M54" s="17"/>
+      <c r="M54" s="23"/>
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D55" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E55" s="15" t="s">
+      <c r="E55" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
-      <c r="H55" s="16"/>
-      <c r="I55" s="16"/>
-      <c r="J55" s="16"/>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="17"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
+      <c r="H55" s="22"/>
+      <c r="I55" s="22"/>
+      <c r="J55" s="22"/>
+      <c r="K55" s="22"/>
+      <c r="L55" s="22"/>
+      <c r="M55" s="23"/>
     </row>
     <row r="56" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D56" s="4" t="s">
@@ -2291,7 +2289,7 @@
         <v>39</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I57" s="11" t="s">
         <v>41</v>
@@ -2317,7 +2315,7 @@
         <v>39</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I58" s="10"/>
       <c r="J58" s="11" t="s">
@@ -2341,7 +2339,7 @@
         <v>39</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="11" t="s">
@@ -2365,7 +2363,7 @@
         <v>39</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I60" s="10"/>
       <c r="J60" s="10"/>
@@ -2387,7 +2385,7 @@
         <v>39</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="10"/>
@@ -2422,68 +2420,68 @@
       <c r="M63" s="14"/>
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D64" s="18" t="s">
+      <c r="D64" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E64" s="19"/>
-      <c r="F64" s="19"/>
-      <c r="G64" s="19"/>
-      <c r="H64" s="19"/>
-      <c r="I64" s="19"/>
-      <c r="J64" s="19"/>
-      <c r="K64" s="19"/>
-      <c r="L64" s="19"/>
-      <c r="M64" s="20"/>
+      <c r="E64" s="25"/>
+      <c r="F64" s="25"/>
+      <c r="G64" s="25"/>
+      <c r="H64" s="25"/>
+      <c r="I64" s="25"/>
+      <c r="J64" s="25"/>
+      <c r="K64" s="25"/>
+      <c r="L64" s="25"/>
+      <c r="M64" s="26"/>
     </row>
     <row r="65" spans="4:13" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D65" s="21" t="s">
+      <c r="D65" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
-      <c r="H65" s="22"/>
-      <c r="I65" s="22"/>
-      <c r="J65" s="22"/>
-      <c r="K65" s="22"/>
-      <c r="L65" s="22"/>
-      <c r="M65" s="23"/>
+      <c r="E65" s="28"/>
+      <c r="F65" s="28"/>
+      <c r="G65" s="28"/>
+      <c r="H65" s="28"/>
+      <c r="I65" s="28"/>
+      <c r="J65" s="28"/>
+      <c r="K65" s="28"/>
+      <c r="L65" s="28"/>
+      <c r="M65" s="29"/>
     </row>
     <row r="66" spans="4:13" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D66" s="24"/>
-      <c r="E66" s="25"/>
-      <c r="F66" s="25"/>
-      <c r="G66" s="25"/>
-      <c r="H66" s="25"/>
-      <c r="I66" s="25"/>
-      <c r="J66" s="25"/>
-      <c r="K66" s="25"/>
-      <c r="L66" s="25"/>
-      <c r="M66" s="26"/>
+      <c r="D66" s="30"/>
+      <c r="E66" s="31"/>
+      <c r="F66" s="31"/>
+      <c r="G66" s="31"/>
+      <c r="H66" s="31"/>
+      <c r="I66" s="31"/>
+      <c r="J66" s="31"/>
+      <c r="K66" s="31"/>
+      <c r="L66" s="31"/>
+      <c r="M66" s="32"/>
     </row>
     <row r="67" spans="4:13" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D67" s="24"/>
-      <c r="E67" s="25"/>
-      <c r="F67" s="25"/>
-      <c r="G67" s="25"/>
-      <c r="H67" s="25"/>
-      <c r="I67" s="25"/>
-      <c r="J67" s="25"/>
-      <c r="K67" s="25"/>
-      <c r="L67" s="25"/>
-      <c r="M67" s="26"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="31"/>
+      <c r="F67" s="31"/>
+      <c r="G67" s="31"/>
+      <c r="H67" s="31"/>
+      <c r="I67" s="31"/>
+      <c r="J67" s="31"/>
+      <c r="K67" s="31"/>
+      <c r="L67" s="31"/>
+      <c r="M67" s="32"/>
     </row>
     <row r="68" spans="4:13" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D68" s="27"/>
-      <c r="E68" s="28"/>
-      <c r="F68" s="28"/>
-      <c r="G68" s="28"/>
-      <c r="H68" s="28"/>
-      <c r="I68" s="28"/>
-      <c r="J68" s="28"/>
-      <c r="K68" s="28"/>
-      <c r="L68" s="28"/>
-      <c r="M68" s="29"/>
+      <c r="D68" s="33"/>
+      <c r="E68" s="34"/>
+      <c r="F68" s="34"/>
+      <c r="G68" s="34"/>
+      <c r="H68" s="34"/>
+      <c r="I68" s="34"/>
+      <c r="J68" s="34"/>
+      <c r="K68" s="34"/>
+      <c r="L68" s="34"/>
+      <c r="M68" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="28">
